--- a/docs/pension_data_combined_2026-09-04.xlsx
+++ b/docs/pension_data_combined_2026-09-04.xlsx
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.2043</v>
+        <v>1.2058</v>
       </c>
       <c r="D39" t="n">
         <v>2837583</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.3941</v>
+        <v>2.3988</v>
       </c>
       <c r="D40" t="n">
         <v>41934549</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2.3729</v>
+        <v>2.3783</v>
       </c>
       <c r="D41" t="n">
         <v>135952962</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.3766</v>
+        <v>2.3813</v>
       </c>
       <c r="D42" t="n">
         <v>336301923</v>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.4062</v>
+        <v>2.4109</v>
       </c>
       <c r="D43" t="n">
         <v>431814357</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.0621</v>
+        <v>2.0646</v>
       </c>
       <c r="D44" t="n">
         <v>347311865</v>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.5597</v>
+        <v>1.5606</v>
       </c>
       <c r="D45" t="n">
         <v>259587531</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.2142</v>
+        <v>1.2146</v>
       </c>
       <c r="D46" t="n">
         <v>56476155</v>
@@ -1228,7 +1228,7 @@
         <v>1.1643</v>
       </c>
       <c r="D48" t="n">
-        <v>3991402.83</v>
+        <v>3991189.65</v>
       </c>
     </row>
     <row r="49">
@@ -1246,7 +1246,7 @@
         <v>2.1811</v>
       </c>
       <c r="D49" t="n">
-        <v>71028892.65000001</v>
+        <v>70998764.83</v>
       </c>
     </row>
     <row r="50">
@@ -1264,7 +1264,7 @@
         <v>2.1999</v>
       </c>
       <c r="D50" t="n">
-        <v>231284121.36</v>
+        <v>231277321.4</v>
       </c>
     </row>
     <row r="51">
@@ -1282,7 +1282,7 @@
         <v>2.2182</v>
       </c>
       <c r="D51" t="n">
-        <v>354232890.92</v>
+        <v>354213195.6</v>
       </c>
     </row>
     <row r="52">
@@ -1300,7 +1300,7 @@
         <v>2.2231</v>
       </c>
       <c r="D52" t="n">
-        <v>432471495.91</v>
+        <v>432403919.6</v>
       </c>
     </row>
     <row r="53">
@@ -1318,7 +1318,7 @@
         <v>1.9848</v>
       </c>
       <c r="D53" t="n">
-        <v>397582105.4</v>
+        <v>397673676.8</v>
       </c>
     </row>
     <row r="54">
@@ -1336,7 +1336,7 @@
         <v>1.5435</v>
       </c>
       <c r="D54" t="n">
-        <v>321040995.33</v>
+        <v>320760217.4</v>
       </c>
     </row>
     <row r="55">
@@ -1354,7 +1354,7 @@
         <v>1.1999</v>
       </c>
       <c r="D55" t="n">
-        <v>59884933.03</v>
+        <v>59774179.7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/pension_data_combined_2026-09-04.xlsx
+++ b/docs/pension_data_combined_2026-09-04.xlsx
@@ -1224,9 +1224,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1.1643</v>
-      </c>
       <c r="D48" t="n">
         <v>3991189.65</v>
       </c>
